--- a/test_data/AWX_Bank_Transfer_testing_v3_Latest.xlsx
+++ b/test_data/AWX_Bank_Transfer_testing_v3_Latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PycharmProjects\FileUploadAutomation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3DC072-0265-4932-9673-858C5C6873E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCD32BF-909B-43C9-A991-2617F6E7ACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1130" yWindow="1020" windowWidth="18070" windowHeight="9780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Payment_Entry" sheetId="1" r:id="rId1"/>
@@ -2310,7 +2310,7 @@
       <c r="H1" s="95"/>
       <c r="I1" s="7">
         <f>SUM(I3:I9955)</f>
-        <v>4605</v>
+        <v>3605</v>
       </c>
       <c r="X1" s="96" t="s">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       <c r="Y1" s="96"/>
       <c r="Z1" s="7">
         <f>SUM(Z3:Z9955)</f>
-        <v>4605</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -2420,7 +2420,7 @@
     <row r="4" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A4" s="19">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>32</v>
@@ -2442,7 +2442,7 @@
         <v>37</v>
       </c>
       <c r="I4" s="5">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="J4" s="2">
         <v>2612145</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Y4" s="22"/>
       <c r="Z4" s="5">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
@@ -2484,7 +2484,7 @@
     <row r="5" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A5" s="19">
         <f t="shared" ref="A5:A13" ca="1" si="1">TODAY()</f>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>32</v>
@@ -2506,7 +2506,7 @@
         <v>40</v>
       </c>
       <c r="I5" s="5">
-        <v>422</v>
+        <v>322</v>
       </c>
       <c r="J5" s="2">
         <v>2612145</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="Y5" s="22"/>
       <c r="Z5" s="5">
-        <v>422</v>
+        <v>322</v>
       </c>
       <c r="AA5" s="22"/>
       <c r="AB5" s="22"/>
@@ -2548,7 +2548,7 @@
     <row r="6" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A6" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>32</v>
@@ -2570,7 +2570,7 @@
         <v>41</v>
       </c>
       <c r="I6" s="5">
-        <v>433</v>
+        <v>333</v>
       </c>
       <c r="J6" s="2">
         <v>2612145</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Y6" s="22"/>
       <c r="Z6" s="5">
-        <v>433</v>
+        <v>333</v>
       </c>
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
@@ -2612,7 +2612,7 @@
     <row r="7" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A7" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>32</v>
@@ -2634,7 +2634,7 @@
         <v>46</v>
       </c>
       <c r="I7" s="5">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="J7" s="2">
         <v>2612145</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Y7" s="22"/>
       <c r="Z7" s="5">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
@@ -2676,7 +2676,7 @@
     <row r="8" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A8" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>32</v>
@@ -2698,7 +2698,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="5">
-        <v>455</v>
+        <v>355</v>
       </c>
       <c r="J8" s="2">
         <v>2612145</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="Y8" s="22"/>
       <c r="Z8" s="5">
-        <v>455</v>
+        <v>355</v>
       </c>
       <c r="AA8" s="22"/>
       <c r="AB8" s="22"/>
@@ -2740,7 +2740,7 @@
     <row r="9" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A9" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>32</v>
@@ -2762,7 +2762,7 @@
         <v>41</v>
       </c>
       <c r="I9" s="5">
-        <v>466</v>
+        <v>366</v>
       </c>
       <c r="J9" s="2">
         <v>2612145</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Y9" s="22"/>
       <c r="Z9" s="5">
-        <v>466</v>
+        <v>366</v>
       </c>
       <c r="AA9" s="22"/>
       <c r="AB9" s="22"/>
@@ -2804,7 +2804,7 @@
     <row r="10" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A10" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>32</v>
@@ -2826,7 +2826,7 @@
         <v>40</v>
       </c>
       <c r="I10" s="5">
-        <v>477</v>
+        <v>377</v>
       </c>
       <c r="J10" s="2">
         <v>2612145</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Y10" s="22"/>
       <c r="Z10" s="5">
-        <v>477</v>
+        <v>377</v>
       </c>
       <c r="AA10" s="22"/>
       <c r="AB10" s="22"/>
@@ -2868,7 +2868,7 @@
     <row r="11" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A11" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>32</v>
@@ -2890,7 +2890,7 @@
         <v>41</v>
       </c>
       <c r="I11" s="5">
-        <v>488</v>
+        <v>388</v>
       </c>
       <c r="J11" s="2">
         <v>2612145</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Y11" s="22"/>
       <c r="Z11" s="5">
-        <v>488</v>
+        <v>388</v>
       </c>
       <c r="AA11" s="22"/>
       <c r="AB11" s="22"/>
@@ -2932,7 +2932,7 @@
     <row r="12" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A12" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B12" s="20" t="s">
         <v>32</v>
@@ -2954,7 +2954,7 @@
         <v>40</v>
       </c>
       <c r="I12" s="5">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="J12" s="2">
         <v>2612145</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="Y12" s="22"/>
       <c r="Z12" s="5">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="AA12" s="22"/>
       <c r="AB12" s="22" t="s">
@@ -2998,7 +2998,7 @@
     <row r="13" spans="1:30" s="28" customFormat="1" ht="16">
       <c r="A13" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>32</v>
@@ -3020,7 +3020,7 @@
         <v>41</v>
       </c>
       <c r="I13" s="5">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="J13" s="2">
         <v>2612145</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Y13" s="22"/>
       <c r="Z13" s="5">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="AA13" s="22"/>
       <c r="AB13" s="22"/>

--- a/test_data/AWX_Bank_Transfer_testing_v3_Latest.xlsx
+++ b/test_data/AWX_Bank_Transfer_testing_v3_Latest.xlsx
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="I4" s="103" t="n">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2612145</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="Y4" s="22" t="n"/>
       <c r="Z4" s="103" t="n">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AA4" s="22" t="n"/>
       <c r="AB4" s="22" t="n"/>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="I5" s="103" t="n">
-        <v>322</v>
+        <v>422</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2612145</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Y5" s="22" t="n"/>
       <c r="Z5" s="103" t="n">
-        <v>322</v>
+        <v>422</v>
       </c>
       <c r="AA5" s="22" t="n"/>
       <c r="AB5" s="22" t="n"/>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="I6" s="103" t="n">
-        <v>333</v>
+        <v>433</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2612145</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Y6" s="22" t="n"/>
       <c r="Z6" s="103" t="n">
-        <v>333</v>
+        <v>433</v>
       </c>
       <c r="AA6" s="22" t="n"/>
       <c r="AB6" s="22" t="n"/>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I7" s="103" t="n">
-        <v>344</v>
+        <v>444</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2612145</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="Y7" s="22" t="n"/>
       <c r="Z7" s="103" t="n">
-        <v>344</v>
+        <v>444</v>
       </c>
       <c r="AA7" s="22" t="n"/>
       <c r="AB7" s="22" t="n"/>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="I8" s="103" t="n">
-        <v>355</v>
+        <v>455</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>2612145</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Y8" s="22" t="n"/>
       <c r="Z8" s="103" t="n">
-        <v>355</v>
+        <v>455</v>
       </c>
       <c r="AA8" s="22" t="n"/>
       <c r="AB8" s="22" t="n"/>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="I9" s="103" t="n">
-        <v>366</v>
+        <v>466</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2612145</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Y9" s="22" t="n"/>
       <c r="Z9" s="103" t="n">
-        <v>366</v>
+        <v>466</v>
       </c>
       <c r="AA9" s="22" t="n"/>
       <c r="AB9" s="22" t="n"/>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="I10" s="103" t="n">
-        <v>377</v>
+        <v>477</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2612145</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Y10" s="22" t="n"/>
       <c r="Z10" s="103" t="n">
-        <v>377</v>
+        <v>477</v>
       </c>
       <c r="AA10" s="22" t="n"/>
       <c r="AB10" s="22" t="n"/>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I11" s="103" t="n">
-        <v>388</v>
+        <v>488</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>2612145</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Y11" s="22" t="n"/>
       <c r="Z11" s="103" t="n">
-        <v>388</v>
+        <v>488</v>
       </c>
       <c r="AA11" s="22" t="n"/>
       <c r="AB11" s="22" t="n"/>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="I12" s="103" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2612145</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Y12" s="22" t="n"/>
       <c r="Z12" s="103" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="AA12" s="22" t="n"/>
       <c r="AB12" s="22" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I13" s="103" t="n">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>2612145</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="Y13" s="22" t="n"/>
       <c r="Z13" s="103" t="n">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AA13" s="22" t="n"/>
       <c r="AB13" s="22" t="n"/>
